--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/OHIO_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/OHIO_2013.xlsx
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C178">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C421">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C479">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C505">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C700">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C779">
